--- a/Projeto1/Trabalho_FSilva_JMarinho/Eficiencia.xlsx
+++ b/Projeto1/Trabalho_FSilva_JMarinho/Eficiencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zemig\Desktop\Material_LEEC\3ºano\2ºsemestre\Redes_de_Computadores\Projetos\Projeto1\Trabalho_FSilva_JMarinho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1530533A-8AF3-450F-B1E8-BE3F426D033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA95C87-DE93-4EDF-9EC3-B10EF0E7509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE881187-D8BB-4B50-89FB-8A15BC262BD9}"/>
+    <workbookView xWindow="11784" yWindow="0" windowWidth="11352" windowHeight="12336" xr2:uid="{BE881187-D8BB-4B50-89FB-8A15BC262BD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,37 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+  <si>
+    <t>Eficiencia VS FER - chunk size = 1024Bytes</t>
+  </si>
+  <si>
+    <t>FER</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>Goodput</t>
+  </si>
+  <si>
+    <t>Eficiencia</t>
+  </si>
+  <si>
+    <t>Emissor</t>
+  </si>
+  <si>
+    <t>Recetor</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -66,8 +95,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +438,363 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BECA7A0-3C9E-4CE9-BBBB-D6614C2A0C85}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <f>1-(1-C6)^(1/1024)</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>955.83</v>
+      </c>
+      <c r="E6">
+        <v>943.8</v>
+      </c>
+      <c r="F6">
+        <v>0.99</v>
+      </c>
+      <c r="G6">
+        <v>944.62</v>
+      </c>
+      <c r="H6">
+        <v>943.59</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <f t="shared" ref="B7:B24" si="0">1-(1-C7)^(1/1024)</f>
+        <v>9.8147329421482965E-6</v>
+      </c>
+      <c r="C7">
+        <v>0.01</v>
+      </c>
+      <c r="D7">
+        <v>955.83</v>
+      </c>
+      <c r="E7">
+        <v>943.79</v>
+      </c>
+      <c r="F7">
+        <v>0.99</v>
+      </c>
+      <c r="G7">
+        <v>944.61</v>
+      </c>
+      <c r="H7">
+        <v>943.57</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9729011745295288E-5</v>
+      </c>
+      <c r="C8">
+        <f>C7+0.01</f>
+        <v>0.02</v>
+      </c>
+      <c r="D8">
+        <v>955.84</v>
+      </c>
+      <c r="E8">
+        <v>943.8</v>
+      </c>
+      <c r="F8">
+        <v>0.99</v>
+      </c>
+      <c r="G8">
+        <v>944.62</v>
+      </c>
+      <c r="H8">
+        <v>943.59</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <f t="shared" si="0"/>
+        <v>2.9744877421689075E-5</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:C16" si="1">C8+0.01</f>
+        <v>0.03</v>
+      </c>
+      <c r="D9">
+        <v>955.92</v>
+      </c>
+      <c r="E9">
+        <v>943.89</v>
+      </c>
+      <c r="F9">
+        <v>0.99</v>
+      </c>
+      <c r="G9">
+        <v>944.69</v>
+      </c>
+      <c r="H9">
+        <v>943.65</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <f t="shared" si="0"/>
+        <v>3.9864434415948224E-5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D10">
+        <v>955.85</v>
+      </c>
+      <c r="E10">
+        <v>943.81</v>
+      </c>
+      <c r="F10">
+        <v>0.99</v>
+      </c>
+      <c r="G10">
+        <v>944.62</v>
+      </c>
+      <c r="H10">
+        <v>943.59</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <f t="shared" si="0"/>
+        <v>5.0089853261714445E-5</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="D11">
+        <v>955.86</v>
+      </c>
+      <c r="E11">
+        <v>943.82</v>
+      </c>
+      <c r="F11">
+        <v>0.99</v>
+      </c>
+      <c r="G11">
+        <v>944.61</v>
+      </c>
+      <c r="H11">
+        <v>943.58</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0423373377860301E-5</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>7.0867306015354181E-5</v>
+      </c>
+      <c r="C13">
+        <f>C12+0.01</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>8.1424037362665125E-5</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>9.209603182125381E-5</v>
+      </c>
+      <c r="C15">
+        <f>C14+0.01</f>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0288583546147478E-4</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <f t="shared" si="0"/>
+        <v>1.586972983390611E-4</v>
+      </c>
+      <c r="C17">
+        <f>C16+0.05</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <f t="shared" si="0"/>
+        <v>2.1788988288096167E-4</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:C24" si="2">C17+0.05</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <f t="shared" si="0"/>
+        <v>2.809000640660031E-4</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <f t="shared" si="0"/>
+        <v>3.4825472018251702E-4</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <f t="shared" si="0"/>
+        <v>4.2059796536286775E-4</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9872874166501102E-4</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>0.39999999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8365480328215202E-4</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <f t="shared" si="0"/>
+        <v>6.7667249734926216E-4</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>0.49999999999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Projeto1/Trabalho_FSilva_JMarinho/Eficiencia.xlsx
+++ b/Projeto1/Trabalho_FSilva_JMarinho/Eficiencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zemig\Desktop\Material_LEEC\3ºano\2ºsemestre\Redes_de_Computadores\Projetos\Projeto1\Trabalho_FSilva_JMarinho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30014485-76F7-4C2D-AF5A-6FCF96C16163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F76F754-6A7E-4FD9-9979-9231C8B7151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE881187-D8BB-4B50-89FB-8A15BC262BD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Eficiencia VS FER - chunk size = 1024Bytes</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>SE (%)</t>
-  </si>
-  <si>
-    <t>SR (%)</t>
   </si>
   <si>
     <t>Influência do tamanho do Frame-I</t>
@@ -64,13 +61,20 @@
   <si>
     <t>SE(%)</t>
   </si>
+  <si>
+    <t>Tamanho (Bytes)</t>
+  </si>
+  <si>
+    <t>Taxa de Bytes uteis</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -101,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -110,7 +114,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -142,6 +154,66 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-PT"/>
+              <a:t>Eficiência (%)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-PT" baseline="0"/>
+              <a:t> em função da probabilidade de erro de frame</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -360,7 +432,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$8:$E$65</c:f>
+              <c:f>Sheet1!$F$8:$F$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="58"/>
@@ -433,12 +505,9 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$5</c:f>
+              <c:f>Sheet1!$G$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SR (%)</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -646,67 +715,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$6:$G$65</c:f>
+              <c:f>Sheet1!$H$6:$H$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
-                <c:pt idx="0">
-                  <c:v>77.816666666666663</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>41.063333333333333</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>77.796666666666667</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>59.196666666666658</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>41.003333333333337</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>41.13</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>54.95333333333334</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>59.34</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>41.13</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>54.25333333333333</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>17.246666666666666</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>32.693333333333335</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>11.18</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2.16</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2.1033333333333335</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.0066666666666666</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -794,6 +806,7 @@
         <c:axId val="1146706079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1006,7 +1019,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$G$71:$G$91</c:f>
+              <c:f>Sheet1!$H$71:$H$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -1036,9 +1049,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$71:$H$91</c:f>
+              <c:f>Sheet1!$I$71:$I$91</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>15.073063333333332</c:v>
@@ -1166,7 +1179,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1366,7 +1379,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$G$71:$G$91</c:f>
+              <c:f>Sheet1!$H$71:$H$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -1396,9 +1409,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$71:$I$91</c:f>
+              <c:f>Sheet1!$J$71:$J$91</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>728.18666666666661</c:v>
@@ -1526,7 +1539,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1721,7 +1734,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$G$71:$G$91</c:f>
+              <c:f>Sheet1!$H$71:$H$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -1751,9 +1764,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$J$71:$J$91</c:f>
+              <c:f>Sheet1!$K$71:$K$91</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>15.170000000000002</c:v>
@@ -1881,7 +1894,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4202,13 +4215,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>220980</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -4238,13 +4251,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>156210</xdr:rowOff>
@@ -4274,13 +4287,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>100</xdr:row>
       <xdr:rowOff>34290</xdr:rowOff>
@@ -4310,13 +4323,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>320040</xdr:colOff>
       <xdr:row>91</xdr:row>
       <xdr:rowOff>87630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>106</xdr:row>
       <xdr:rowOff>87630</xdr:rowOff>
@@ -4664,30 +4677,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BECA7A0-3C9E-4CE9-BBBB-D6614C2A0C85}">
-  <dimension ref="B3:L91"/>
+  <dimension ref="B3:Z91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="36.77734375" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4695,19 +4712,23 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
       </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
       <c r="F5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>0</v>
       </c>
@@ -4715,18 +4736,15 @@
         <v>77.790000000000006</v>
       </c>
       <c r="E6" s="3">
+        <f>AVERAGE(C6:C8)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
         <f>AVERAGE(D6:D8)</f>
         <v>77.806666666666672</v>
       </c>
-      <c r="F6">
-        <v>77.8</v>
-      </c>
-      <c r="G6" s="3">
-        <f>AVERAGE(F6:F8)</f>
-        <v>77.816666666666663</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>0</v>
       </c>
@@ -4734,12 +4752,9 @@
         <v>77.819999999999993</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7">
-        <v>77.83</v>
-      </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>0</v>
       </c>
@@ -4747,12 +4762,9 @@
         <v>77.81</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8">
-        <v>77.819999999999993</v>
-      </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9">
         <v>0.01</v>
@@ -4761,18 +4773,15 @@
         <v>23.87</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" ref="E9" si="0">AVERAGE(D9:D11)</f>
+        <f t="shared" ref="E9" si="0">AVERAGE(C9:C11)</f>
+        <v>0.01</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" ref="F9" si="1">AVERAGE(D9:D11)</f>
         <v>42.266666666666666</v>
       </c>
-      <c r="F9">
-        <v>22.39</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" ref="G9" si="1">AVERAGE(F9:F11)</f>
-        <v>41.063333333333333</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10">
         <v>0.01</v>
@@ -4781,12 +4790,9 @@
         <v>25.11</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10">
-        <v>22.97</v>
-      </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11">
         <v>0.01</v>
@@ -4795,12 +4801,9 @@
         <v>77.819999999999993</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11">
-        <v>77.83</v>
-      </c>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12">
         <v>0.02</v>
@@ -4809,18 +4812,15 @@
         <v>77.77</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12" si="2">AVERAGE(D12:D14)</f>
+        <f t="shared" ref="E12" si="2">AVERAGE(C12:C14)</f>
+        <v>0.02</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" ref="F12" si="3">AVERAGE(D12:D14)</f>
         <v>77.793333333333337</v>
       </c>
-      <c r="F12">
-        <v>77.77</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" ref="G12" si="3">AVERAGE(F12:F14)</f>
-        <v>77.796666666666667</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13">
         <v>0.02</v>
@@ -4829,12 +4829,9 @@
         <v>77.8</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13">
-        <v>77.81</v>
-      </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14">
         <v>0.02</v>
@@ -4843,12 +4840,9 @@
         <v>77.81</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14">
-        <v>77.81</v>
-      </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15">
         <v>0.03</v>
@@ -4857,18 +4851,15 @@
         <v>77.8</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" ref="E15" si="4">AVERAGE(D15:D17)</f>
+        <f t="shared" ref="E15" si="4">AVERAGE(C15:C17)</f>
+        <v>0.03</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" ref="F15" si="5">AVERAGE(D15:D17)</f>
         <v>59.876666666666665</v>
       </c>
-      <c r="F15">
-        <v>77.81</v>
-      </c>
-      <c r="G15" s="3">
-        <f t="shared" ref="G15" si="5">AVERAGE(F15:F17)</f>
-        <v>59.196666666666658</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16">
         <v>0.03</v>
@@ -4877,12 +4868,9 @@
         <v>77.760000000000005</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16">
-        <v>77.77</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17">
         <v>0.03</v>
@@ -4891,12 +4879,9 @@
         <v>24.07</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17">
-        <v>22.01</v>
-      </c>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18">
         <v>0.04</v>
@@ -4905,18 +4890,15 @@
         <v>77.8</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" ref="E18" si="6">AVERAGE(D18:D20)</f>
+        <f t="shared" ref="E18" si="6">AVERAGE(C18:C20)</f>
+        <v>0.04</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" ref="F18" si="7">AVERAGE(D18:D20)</f>
         <v>41.50333333333333</v>
       </c>
-      <c r="F18">
-        <v>77.81</v>
-      </c>
-      <c r="G18" s="3">
-        <f t="shared" ref="G18" si="7">AVERAGE(F18:F20)</f>
-        <v>41.003333333333337</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19">
         <v>0.04</v>
@@ -4925,12 +4907,9 @@
         <v>23.88</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19">
-        <v>22.39</v>
-      </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20">
         <v>0.04</v>
@@ -4939,12 +4918,9 @@
         <v>22.83</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20">
-        <v>22.81</v>
-      </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21">
         <v>0.05</v>
@@ -4953,18 +4929,15 @@
         <v>77.78</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" ref="E21" si="8">AVERAGE(D21:D23)</f>
+        <f t="shared" ref="E21" si="8">AVERAGE(C21:C23)</f>
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" ref="F21" si="9">AVERAGE(D21:D23)</f>
         <v>42.546666666666667</v>
       </c>
-      <c r="F21">
-        <v>77.78</v>
-      </c>
-      <c r="G21" s="3">
-        <f t="shared" ref="G21" si="9">AVERAGE(F21:F23)</f>
-        <v>41.13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="2"/>
       <c r="C22">
         <v>0.05</v>
@@ -4973,12 +4946,9 @@
         <v>25.05</v>
       </c>
       <c r="E22" s="3"/>
-      <c r="F22">
-        <v>22.92</v>
-      </c>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
       <c r="C23">
         <v>0.05</v>
@@ -4987,12 +4957,9 @@
         <v>24.81</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23">
-        <v>22.69</v>
-      </c>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="2"/>
       <c r="C24">
         <v>0.06</v>
@@ -5001,18 +4968,15 @@
         <v>77.790000000000006</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" ref="E24" si="10">AVERAGE(D24:D26)</f>
+        <f t="shared" ref="E24" si="10">AVERAGE(C24:C26)</f>
+        <v>0.06</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" ref="F24" si="11">AVERAGE(D24:D26)</f>
         <v>55.646666666666668</v>
       </c>
-      <c r="F24">
-        <v>77.8</v>
-      </c>
-      <c r="G24" s="3">
-        <f t="shared" ref="G24" si="11">AVERAGE(F24:F26)</f>
-        <v>54.95333333333334</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
       <c r="C25">
         <v>0.06</v>
@@ -5021,12 +4985,9 @@
         <v>77.78</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25">
-        <v>77.790000000000006</v>
-      </c>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="2"/>
       <c r="C26">
         <v>0.06</v>
@@ -5035,12 +4996,9 @@
         <v>11.37</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26">
-        <v>9.27</v>
-      </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27">
         <v>7.0000000000000007E-2</v>
@@ -5049,18 +5007,15 @@
         <v>77.790000000000006</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" ref="E27" si="12">AVERAGE(D27:D29)</f>
+        <f t="shared" ref="E27" si="12">AVERAGE(C27:C29)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" ref="F27" si="13">AVERAGE(D27:D29)</f>
         <v>60.036666666666669</v>
       </c>
-      <c r="F27">
-        <v>77.790000000000006</v>
-      </c>
-      <c r="G27" s="3">
-        <f t="shared" ref="G27" si="13">AVERAGE(F27:F29)</f>
-        <v>59.34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="2"/>
       <c r="C28">
         <v>7.0000000000000007E-2</v>
@@ -5069,12 +5024,9 @@
         <v>77.75</v>
       </c>
       <c r="E28" s="3"/>
-      <c r="F28">
-        <v>77.760000000000005</v>
-      </c>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29">
         <v>7.0000000000000007E-2</v>
@@ -5083,12 +5035,9 @@
         <v>24.57</v>
       </c>
       <c r="E29" s="3"/>
-      <c r="F29">
-        <v>22.47</v>
-      </c>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="2"/>
       <c r="C30">
         <v>0.08</v>
@@ -5097,18 +5046,15 @@
         <v>25.01</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" ref="E30" si="14">AVERAGE(D30:D32)</f>
+        <f>AVERAGE(C30:C32)</f>
+        <v>0.08</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" ref="F30" si="14">AVERAGE(D30:D32)</f>
         <v>42.543333333333329</v>
       </c>
-      <c r="F30">
-        <v>22.88</v>
-      </c>
-      <c r="G30" s="3">
-        <f t="shared" ref="G30" si="15">AVERAGE(F30:F32)</f>
-        <v>41.13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="C31">
         <v>0.08</v>
@@ -5117,12 +5063,9 @@
         <v>24.87</v>
       </c>
       <c r="E31" s="3"/>
-      <c r="F31">
-        <v>22.75</v>
-      </c>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="C32">
         <v>0.08</v>
@@ -5131,12 +5074,9 @@
         <v>77.75</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32">
-        <v>77.760000000000005</v>
-      </c>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="2"/>
       <c r="C33">
         <v>0.09</v>
@@ -5145,18 +5085,15 @@
         <v>77.8</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" ref="E33" si="16">AVERAGE(D33:D35)</f>
+        <f t="shared" ref="E33" si="15">AVERAGE(C33:C35)</f>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" ref="F33" si="16">AVERAGE(D33:D35)</f>
         <v>55.146666666666668</v>
       </c>
-      <c r="F33">
-        <v>77.81</v>
-      </c>
-      <c r="G33" s="3">
-        <f t="shared" ref="G33" si="17">AVERAGE(F33:F35)</f>
-        <v>54.25333333333333</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="C34">
         <v>0.09</v>
@@ -5165,12 +5102,9 @@
         <v>9.91</v>
       </c>
       <c r="E34" s="3"/>
-      <c r="F34">
-        <v>7.21</v>
-      </c>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>
       <c r="C35">
         <v>0.09</v>
@@ -5179,12 +5113,9 @@
         <v>77.73</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35">
-        <v>77.739999999999995</v>
-      </c>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="2"/>
       <c r="C36">
         <v>0.1</v>
@@ -5193,18 +5124,15 @@
         <v>24.68</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" ref="E36" si="18">AVERAGE(D36:D38)</f>
+        <f t="shared" ref="E36" si="17">AVERAGE(C36:C38)</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" ref="F36" si="18">AVERAGE(D36:D38)</f>
         <v>19.080000000000002</v>
       </c>
-      <c r="F36">
-        <v>22.58</v>
-      </c>
-      <c r="G36" s="3">
-        <f t="shared" ref="G36" si="19">AVERAGE(F36:F38)</f>
-        <v>17.246666666666666</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="2"/>
       <c r="C37">
         <v>0.1</v>
@@ -5213,12 +5141,9 @@
         <v>24.03</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37">
-        <v>21.98</v>
-      </c>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="2"/>
       <c r="C38">
         <v>0.1</v>
@@ -5227,12 +5152,9 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38">
-        <v>7.18</v>
-      </c>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="2"/>
       <c r="C39">
         <v>0.2</v>
@@ -5241,18 +5163,15 @@
         <v>15.57</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" ref="E39" si="20">AVERAGE(D39:D41)</f>
+        <f t="shared" ref="E39" si="19">AVERAGE(C39:C41)</f>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" ref="F39" si="20">AVERAGE(D39:D41)</f>
         <v>34.396666666666668</v>
       </c>
-      <c r="F39">
-        <v>13.12</v>
-      </c>
-      <c r="G39" s="3">
-        <f t="shared" ref="G39" si="21">AVERAGE(F39:F41)</f>
-        <v>32.693333333333335</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="2"/>
       <c r="C40">
         <v>0.2</v>
@@ -5261,12 +5180,9 @@
         <v>77.8</v>
       </c>
       <c r="E40" s="3"/>
-      <c r="F40">
-        <v>77.81</v>
-      </c>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="C41">
         <v>0.2</v>
@@ -5275,12 +5191,9 @@
         <v>9.82</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41">
-        <v>7.15</v>
-      </c>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="2"/>
       <c r="C42">
         <v>0.3</v>
@@ -5289,18 +5202,15 @@
         <v>15.8</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" ref="E42" si="22">AVERAGE(D42:D44)</f>
+        <f>AVERAGE(C42:C44)</f>
+        <v>0.3</v>
+      </c>
+      <c r="F42" s="3">
+        <f t="shared" ref="F42" si="21">AVERAGE(D42:D44)</f>
         <v>13.433333333333332</v>
       </c>
-      <c r="F42">
-        <v>13.32</v>
-      </c>
-      <c r="G42" s="3">
-        <f t="shared" ref="G42" si="23">AVERAGE(F42:F44)</f>
-        <v>11.18</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="2"/>
       <c r="C43">
         <v>0.3</v>
@@ -5309,12 +5219,9 @@
         <v>15.43</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43">
-        <v>13.01</v>
-      </c>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="2"/>
       <c r="C44">
         <v>0.3</v>
@@ -5323,12 +5230,9 @@
         <v>9.07</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44">
-        <v>7.21</v>
-      </c>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C45">
         <v>0.4</v>
       </c>
@@ -5336,18 +5240,15 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" ref="E45" si="24">AVERAGE(D45:D47)</f>
+        <f t="shared" ref="E45" si="22">AVERAGE(C45:C47)</f>
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="F45" s="3">
+        <f t="shared" ref="F45" si="23">AVERAGE(D45:D47)</f>
         <v>3.956666666666667</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <f t="shared" ref="G45" si="25">AVERAGE(F45:F47)</f>
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C46">
         <v>0.4</v>
       </c>
@@ -5355,12 +5256,9 @@
         <v>5.36</v>
       </c>
       <c r="E46" s="3"/>
-      <c r="F46">
-        <v>2.75</v>
-      </c>
-      <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C47">
         <v>0.4</v>
       </c>
@@ -5368,12 +5266,9 @@
         <v>6.51</v>
       </c>
       <c r="E47" s="3"/>
-      <c r="F47">
-        <v>3.73</v>
-      </c>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C48">
         <v>0.5</v>
       </c>
@@ -5381,18 +5276,15 @@
         <v>6.55</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" ref="E48" si="26">AVERAGE(D48:D50)</f>
+        <f t="shared" ref="E48" si="24">AVERAGE(C48:C50)</f>
+        <v>0.5</v>
+      </c>
+      <c r="F48" s="3">
+        <f t="shared" ref="F48" si="25">AVERAGE(D48:D50)</f>
         <v>3.92</v>
       </c>
-      <c r="F48">
-        <v>3.75</v>
-      </c>
-      <c r="G48" s="3">
-        <f t="shared" ref="G48" si="27">AVERAGE(F48:F50)</f>
-        <v>2.1033333333333335</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C49">
         <v>0.5</v>
       </c>
@@ -5400,12 +5292,9 @@
         <v>0</v>
       </c>
       <c r="E49" s="3"/>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C50">
         <v>0.5</v>
       </c>
@@ -5413,12 +5302,9 @@
         <v>5.21</v>
       </c>
       <c r="E50" s="3"/>
-      <c r="F50">
-        <v>2.56</v>
-      </c>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C51">
         <v>0.6</v>
       </c>
@@ -5426,18 +5312,15 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" ref="E51:E60" si="28">AVERAGE(D51:D53)</f>
+        <f t="shared" ref="E51" si="26">AVERAGE(C51:C53)</f>
+        <v>0.6</v>
+      </c>
+      <c r="F51" s="3">
+        <f t="shared" ref="F51:F60" si="27">AVERAGE(D51:D53)</f>
         <v>1.9433333333333334</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3">
-        <f t="shared" ref="G51:G60" si="29">AVERAGE(F51:F53)</f>
-        <v>1.0066666666666666</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C52">
         <v>0.6</v>
       </c>
@@ -5445,12 +5328,9 @@
         <v>5.83</v>
       </c>
       <c r="E52" s="3"/>
-      <c r="F52">
-        <v>3.02</v>
-      </c>
-      <c r="G52" s="3"/>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>0.6</v>
       </c>
@@ -5458,12 +5338,9 @@
         <v>0</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C54">
         <v>0.7</v>
       </c>
@@ -5471,18 +5348,15 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E54" si="28">AVERAGE(C54:C56)</f>
+        <v>0.69999999999999984</v>
+      </c>
+      <c r="F54" s="3">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C55">
         <v>0.7</v>
       </c>
@@ -5490,12 +5364,9 @@
         <v>0</v>
       </c>
       <c r="E55" s="3"/>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C56">
         <v>0.7</v>
       </c>
@@ -5503,12 +5374,9 @@
         <v>0</v>
       </c>
       <c r="E56" s="3"/>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56" s="3"/>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C57">
         <v>0.8</v>
       </c>
@@ -5516,18 +5384,15 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
-        <f t="shared" si="28"/>
+        <f>AVERAGE(C57:C59)</f>
+        <v>0.80000000000000016</v>
+      </c>
+      <c r="F57" s="3">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C58">
         <v>0.8</v>
       </c>
@@ -5535,12 +5400,9 @@
         <v>0</v>
       </c>
       <c r="E58" s="3"/>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3"/>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F58" s="3"/>
+    </row>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C59">
         <v>0.8</v>
       </c>
@@ -5548,12 +5410,9 @@
         <v>0</v>
       </c>
       <c r="E59" s="3"/>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3"/>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F59" s="3"/>
+    </row>
+    <row r="60" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C60">
         <v>0.9</v>
       </c>
@@ -5561,18 +5420,15 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E60" si="29">AVERAGE(C60:C62)</f>
+        <v>0.9</v>
+      </c>
+      <c r="F60" s="3">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C61">
         <v>0.9</v>
       </c>
@@ -5580,12 +5436,9 @@
         <v>0</v>
       </c>
       <c r="E61" s="3"/>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3"/>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F61" s="3"/>
+    </row>
+    <row r="62" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C62">
         <v>0.9</v>
       </c>
@@ -5593,602 +5446,610 @@
         <v>0</v>
       </c>
       <c r="E62" s="3"/>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3"/>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E63" s="3"/>
-      <c r="G63" s="3"/>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E64" s="3"/>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="E65" s="3"/>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="69" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="F62" s="3"/>
+    </row>
+    <row r="63" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="F63" s="3"/>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="F64" s="3"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="F65" s="3"/>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="69" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C69" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-    </row>
-    <row r="70" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="K69" s="3"/>
+    </row>
+    <row r="70" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
         <v>5</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
         <v>6</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>7</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>8</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>5</v>
       </c>
-      <c r="H70" t="s">
-        <v>6</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K70" t="s">
         <v>7</v>
       </c>
-      <c r="J70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C71">
         <v>4</v>
       </c>
       <c r="D71">
         <v>15.08121</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>727.79</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>15.16</v>
       </c>
-      <c r="G71" s="3">
-        <f t="shared" ref="G71" si="30">AVERAGE(C71:C73)</f>
+      <c r="H71" s="3">
+        <f t="shared" ref="H71" si="30">AVERAGE(C71:C73)</f>
         <v>4</v>
       </c>
-      <c r="H71" s="3">
-        <f t="shared" ref="H71" si="31">AVERAGE(D71:D73)</f>
+      <c r="I71" s="5">
+        <f t="shared" ref="I71" si="31">AVERAGE(D71:D73)</f>
         <v>15.073063333333332</v>
       </c>
-      <c r="I71" s="3">
-        <f t="shared" ref="I71:J71" si="32">AVERAGE(E71:E73)</f>
+      <c r="J71" s="4">
+        <f t="shared" ref="J71:K71" si="32">AVERAGE(F71:F73)</f>
         <v>728.18666666666661</v>
       </c>
-      <c r="J71" s="3">
+      <c r="K71" s="4">
         <f t="shared" si="32"/>
         <v>15.170000000000002</v>
       </c>
     </row>
-    <row r="72" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C72">
         <v>4</v>
       </c>
       <c r="D72">
         <v>15.05303</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>729.16</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>15.19</v>
       </c>
-      <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-    </row>
-    <row r="73" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I72" s="5"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C73">
         <v>4</v>
       </c>
       <c r="D73">
         <v>15.084949999999999</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>727.61</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>15.16</v>
       </c>
-      <c r="G73" s="3"/>
       <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-    </row>
-    <row r="74" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I73" s="5"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="W73" s="6"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="8"/>
+      <c r="Z73" s="8"/>
+    </row>
+    <row r="74" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C74">
         <v>16</v>
       </c>
       <c r="D74">
         <v>5.9103700000000003</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>1857.07</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>38.69</v>
       </c>
-      <c r="G74" s="3">
-        <f t="shared" ref="G74" si="33">AVERAGE(C74:C76)</f>
+      <c r="H74" s="3">
+        <f t="shared" ref="H74" si="33">AVERAGE(C74:C76)</f>
         <v>16</v>
       </c>
-      <c r="H74" s="3">
-        <f t="shared" ref="H74" si="34">AVERAGE(D74:D76)</f>
+      <c r="I74" s="5">
+        <f t="shared" ref="I74" si="34">AVERAGE(D74:D76)</f>
         <v>5.9008766666666661</v>
       </c>
-      <c r="I74" s="3">
-        <f t="shared" ref="I74:J74" si="35">AVERAGE(E74:E76)</f>
+      <c r="J74" s="4">
+        <f t="shared" ref="J74:K74" si="35">AVERAGE(F74:F76)</f>
         <v>1860.0766666666666</v>
       </c>
-      <c r="J74" s="3">
+      <c r="K74" s="4">
         <f t="shared" si="35"/>
         <v>38.75333333333333</v>
       </c>
-    </row>
-    <row r="75" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="W74" s="6"/>
+      <c r="X74" s="7"/>
+      <c r="Y74" s="8"/>
+      <c r="Z74" s="8"/>
+    </row>
+    <row r="75" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C75">
         <v>16</v>
       </c>
       <c r="D75">
         <v>5.9134900000000004</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>1856.1</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>38.67</v>
       </c>
-      <c r="G75" s="3"/>
       <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-    </row>
-    <row r="76" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I75" s="5"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="W75" s="6"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="8"/>
+      <c r="Z75" s="8"/>
+    </row>
+    <row r="76" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C76">
         <v>16</v>
       </c>
       <c r="D76">
         <v>5.8787700000000003</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>1867.06</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>38.9</v>
       </c>
-      <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-    </row>
-    <row r="77" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I76" s="5"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C77">
         <v>64</v>
       </c>
       <c r="D77">
         <v>3.6248300000000002</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>3028</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>63.08</v>
       </c>
-      <c r="G77" s="3">
+      <c r="H77" s="3">
         <f>AVERAGE(C77:C79)</f>
         <v>64</v>
       </c>
-      <c r="H77" s="3">
-        <f t="shared" ref="H77:I77" si="36">AVERAGE(D77:D79)</f>
+      <c r="I77" s="5">
+        <f>AVERAGE(D77:D79)</f>
         <v>3.6294733333333333</v>
       </c>
-      <c r="I77" s="3">
-        <f t="shared" si="36"/>
+      <c r="J77" s="4">
+        <f t="shared" ref="J77" si="36">AVERAGE(F77:F79)</f>
         <v>3024.1333333333332</v>
       </c>
-      <c r="J77" s="3">
-        <f>AVERAGE(F77:F79)</f>
+      <c r="K77" s="4">
+        <f>AVERAGE(G77:G79)</f>
         <v>63.00333333333333</v>
       </c>
     </row>
-    <row r="78" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C78">
         <v>64</v>
       </c>
       <c r="D78">
         <v>3.6279400000000002</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>3025.41</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>63.03</v>
       </c>
-      <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I78" s="5"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+    </row>
+    <row r="79" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C79">
         <v>64</v>
       </c>
       <c r="D79">
         <v>3.63565</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>3018.99</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>62.9</v>
       </c>
-      <c r="G79" s="3"/>
       <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I79" s="5"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C80">
         <v>256</v>
       </c>
       <c r="D80">
         <v>3.0715599999999998</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>3573.42</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>74.45</v>
       </c>
-      <c r="G80" s="3">
-        <f t="shared" ref="G80" si="37">AVERAGE(C80:C82)</f>
+      <c r="H80" s="3">
+        <f t="shared" ref="H80" si="37">AVERAGE(C80:C82)</f>
         <v>256</v>
       </c>
-      <c r="H80" s="3">
-        <f t="shared" ref="H80" si="38">AVERAGE(D80:D82)</f>
+      <c r="I80" s="5">
+        <f t="shared" ref="I80" si="38">AVERAGE(D80:D82)</f>
         <v>3.072283333333333</v>
       </c>
-      <c r="I80" s="3">
-        <f t="shared" ref="I80:J80" si="39">AVERAGE(E80:E82)</f>
+      <c r="J80" s="4">
+        <f t="shared" ref="J80:K80" si="39">AVERAGE(F80:F82)</f>
         <v>3572.5833333333335</v>
       </c>
-      <c r="J80" s="3">
+      <c r="K80" s="4">
         <f t="shared" si="39"/>
         <v>74.430000000000007</v>
       </c>
     </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C81">
         <v>256</v>
       </c>
       <c r="D81">
         <v>3.0739299999999998</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>3570.67</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>74.39</v>
       </c>
-      <c r="G81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I81" s="5"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C82">
         <v>256</v>
       </c>
       <c r="D82">
         <v>3.0713599999999999</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>3573.66</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>74.45</v>
       </c>
-      <c r="G82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I82" s="5"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+    </row>
+    <row r="83" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C83">
         <v>1024</v>
       </c>
       <c r="D83">
         <v>2.9344299999999999</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>3788.12</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>77.930000000000007</v>
       </c>
-      <c r="G83" s="3">
-        <f t="shared" ref="G83" si="40">AVERAGE(C83:C85)</f>
+      <c r="H83" s="3">
+        <f t="shared" ref="H83" si="40">AVERAGE(C83:C85)</f>
         <v>1024</v>
       </c>
-      <c r="H83" s="3">
-        <f t="shared" ref="H83" si="41">AVERAGE(D83:D85)</f>
+      <c r="I83" s="5">
+        <f t="shared" ref="I83" si="41">AVERAGE(D83:D85)</f>
         <v>2.9338766666666665</v>
       </c>
-      <c r="I83" s="3">
-        <f t="shared" ref="I83:J83" si="42">AVERAGE(E83:E85)</f>
+      <c r="J83" s="4">
+        <f t="shared" ref="J83:K83" si="42">AVERAGE(F83:F85)</f>
         <v>3757.0266666666666</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="4">
         <f t="shared" si="42"/>
         <v>77.943333333333328</v>
       </c>
     </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C84">
         <v>1024</v>
       </c>
       <c r="D84">
         <v>2.9335300000000002</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>3741.57</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>77.95</v>
       </c>
-      <c r="G84" s="3"/>
       <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-    </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I84" s="5"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+    </row>
+    <row r="85" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C85">
         <v>1024</v>
       </c>
       <c r="D85">
         <v>2.9336700000000002</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>3741.39</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>77.95</v>
       </c>
-      <c r="G85" s="3"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I85" s="5"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C86">
         <v>4096</v>
       </c>
       <c r="D86">
         <v>2.9022700000000001</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>3781.87</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>78.790000000000006</v>
       </c>
-      <c r="G86" s="3">
-        <f t="shared" ref="G86" si="43">AVERAGE(C86:C88)</f>
+      <c r="H86" s="3">
+        <f t="shared" ref="H86" si="43">AVERAGE(C86:C88)</f>
         <v>4096</v>
       </c>
-      <c r="H86" s="3">
-        <f t="shared" ref="H86" si="44">AVERAGE(D86:D88)</f>
+      <c r="I86" s="5">
+        <f t="shared" ref="I86" si="44">AVERAGE(D86:D88)</f>
         <v>2.9019300000000001</v>
       </c>
-      <c r="I86" s="3">
-        <f t="shared" ref="I86:J86" si="45">AVERAGE(E86:E88)</f>
+      <c r="J86" s="4">
+        <f t="shared" ref="J86:K86" si="45">AVERAGE(F86:F88)</f>
         <v>3782.31</v>
       </c>
-      <c r="J86" s="3">
+      <c r="K86" s="4">
         <f t="shared" si="45"/>
         <v>78.8</v>
       </c>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C87">
         <v>4096</v>
       </c>
       <c r="D87">
         <v>2.9005200000000002</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>3784.15</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>78.84</v>
       </c>
-      <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I87" s="5"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C88">
         <v>4096</v>
       </c>
       <c r="D88">
         <v>2.903</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>3780.91</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>78.77</v>
       </c>
-      <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-    </row>
-    <row r="89" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I88" s="5"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C89">
         <v>16384</v>
       </c>
       <c r="D89">
         <v>2.8924500000000002</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>3794.71</v>
       </c>
-      <c r="F89">
+      <c r="G89">
         <v>79.06</v>
       </c>
-      <c r="G89" s="3">
-        <f t="shared" ref="G89" si="46">AVERAGE(C89:C91)</f>
+      <c r="H89" s="3">
+        <f t="shared" ref="H89" si="46">AVERAGE(C89:C91)</f>
         <v>16384</v>
       </c>
-      <c r="H89" s="3">
-        <f t="shared" ref="H89" si="47">AVERAGE(D89:D91)</f>
+      <c r="I89" s="5">
+        <f t="shared" ref="I89" si="47">AVERAGE(D89:D91)</f>
         <v>2.8921833333333336</v>
       </c>
-      <c r="I89" s="3">
-        <f t="shared" ref="I89:J89" si="48">AVERAGE(E89:E91)</f>
+      <c r="J89" s="4">
+        <f t="shared" ref="J89:K89" si="48">AVERAGE(F89:F91)</f>
         <v>3795.06</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="4">
         <f t="shared" si="48"/>
         <v>79.066666666666663</v>
       </c>
     </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C90">
         <v>16384</v>
       </c>
       <c r="D90">
         <v>2.8920599999999999</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>3795.22</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>79.069999999999993</v>
       </c>
-      <c r="G90" s="3"/>
       <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-    </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I90" s="5"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+    </row>
+    <row r="91" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C91">
         <v>16384</v>
       </c>
       <c r="D91">
         <v>2.8920400000000002</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>3795.25</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>79.069999999999993</v>
       </c>
-      <c r="G91" s="3"/>
       <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="G86:G88"/>
     <mergeCell ref="H86:H88"/>
     <mergeCell ref="I86:I88"/>
     <mergeCell ref="J86:J88"/>
-    <mergeCell ref="G89:G91"/>
+    <mergeCell ref="K86:K88"/>
     <mergeCell ref="H89:H91"/>
     <mergeCell ref="I89:I91"/>
     <mergeCell ref="J89:J91"/>
-    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="K89:K91"/>
     <mergeCell ref="H80:H82"/>
     <mergeCell ref="I80:I82"/>
     <mergeCell ref="J80:J82"/>
-    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="K80:K82"/>
     <mergeCell ref="H83:H85"/>
     <mergeCell ref="I83:I85"/>
     <mergeCell ref="J83:J85"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="K83:K85"/>
     <mergeCell ref="I77:I79"/>
     <mergeCell ref="J77:J79"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="K77:K79"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="H69:K69"/>
     <mergeCell ref="H71:H73"/>
     <mergeCell ref="I71:I73"/>
     <mergeCell ref="J71:J73"/>
-    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="K71:K73"/>
     <mergeCell ref="H74:H76"/>
     <mergeCell ref="I74:I76"/>
     <mergeCell ref="J74:J76"/>
+    <mergeCell ref="K74:K76"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="F60:F62"/>
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="E57:E59"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="E63:E65"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="E48:E50"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="E54:E56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
